--- a/Mainstream Framework Integration/scipy_agent/samples/sales.xlsx
+++ b/Mainstream Framework Integration/scipy_agent/samples/sales.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,13 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zxyxi\PycharmProjects\PythonProject3\temp3\excel_agent\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C15E13F-ADFC-42BB-965C-72E7DB0594E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="10"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Evaluation Warning" sheetId="2" r:id="rId4"/>
+    <sheet name="Evaluation Warning (1)" sheetId="3" r:id="rId5"/>
+    <sheet name="Evaluation Warning (2)" sheetId="4" r:id="rId6"/>
+    <sheet name="Evaluation Warning (3)" sheetId="5" r:id="rId7"/>
+    <sheet name="Evaluation Warning (4)" sheetId="6" r:id="rId8"/>
+    <sheet name="Evaluation Warning (5)" sheetId="7" r:id="rId9"/>
+    <sheet name="Evaluation Warning (6)" sheetId="8" r:id="rId10"/>
+    <sheet name="Evaluation Warning (7)" sheetId="9" r:id="rId11"/>
+    <sheet name="Evaluation Warning (8)" sheetId="10" r:id="rId12"/>
+    <sheet name="Evaluation Warning (9)" sheetId="11" r:id="rId13"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,20 +35,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="3">
   <si>
     <t>Sales</t>
   </si>
   <si>
     <t>Year</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evaluation Only. Created with Aspose.Cells for Python via .NET. Copyright 2003 - 2026 Aspose Pty Ltd.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -47,10 +59,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -63,20 +82,33 @@
     </font>
     <font>
       <b/>
+      <i/>
+      <sz val="18"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -88,26 +120,149 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -381,22 +536,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="13.8">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="13.8">
       <c r="A2" s="2">
         <v>2</v>
       </c>
@@ -404,7 +559,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="13.8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -412,7 +567,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="13.8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -420,7 +575,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="13.8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -428,7 +583,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="13.8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -436,7 +591,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="13.8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -444,7 +599,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="13.8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -452,15 +607,15 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="13.8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="4">
         <v>343535130</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="13.8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -468,7 +623,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="13.8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -476,7 +631,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="13.8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -484,7 +639,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="13.8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -492,7 +647,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="13.8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -500,7 +655,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="13.8">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -508,7 +663,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="13.8">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -516,7 +671,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="13.8">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -525,7 +680,156 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09AB1952-7AF2-4912-B4C2-A8AD1AF3BAA4}">
+  <dimension ref="A5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23051156-A33C-4F3A-B9C6-40E56755BAA4}">
+  <dimension ref="A5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+      <c r="A5" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17BE3EF-E592-41C5-A8F6-258DEA5FBAA4}">
+  <dimension ref="A5"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetData>
+    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09EB0175-DBB1-4700-A605-B6F074E4BAA4}">
+  <dimension ref="A5"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetData>
+    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0989F843-6A46-4682-9961-AFDF0A23BAA4}">
+  <dimension ref="A5"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetData>
+    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60412812-57B9-44B3-80D6-1F6AD2EFBAA4}">
+  <dimension ref="A5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+      <c r="A5" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB7FB592-470D-495F-8C67-85CCBF8FBAA4}">
+  <dimension ref="A5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+      <c r="A5" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D7B0B9C-B577-4DBF-805A-85E99A23BAA4}">
+  <dimension ref="A5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+      <c r="A5" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E72FF23-501F-4BC2-A3C0-B7A16855BAA4}">
+  <dimension ref="A5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+      <c r="A5" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7CE4B36-78D7-4E71-8AFF-CBDE401BBAA4}">
+  <dimension ref="A5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="5" spans="1:1" ht="23.25" customHeight="1">
+      <c r="A5" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>